--- a/data/numeric/input/old_data_52/2023-2024-2优质课堂听课记录2024.6.23.xlsx
+++ b/data/numeric/input/old_data_52/2023-2024-2优质课堂听课记录2024.6.23.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0205/ai办公标注/input/old_data_52/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A963775-230F-E846-B7DD-BF7F5EE86419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27340DE0-BBA8-5548-BF61-8FC9CFC55009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35840" yWindow="1300" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,11 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,6 +40,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="278">
   <si>
+    <t>公司A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>序号</t>
   </si>
   <si>
@@ -88,12 +95,27 @@
     <t>1</t>
   </si>
   <si>
+    <t>教师A</t>
+  </si>
+  <si>
+    <t>教师AE</t>
+  </si>
+  <si>
+    <t>学院A</t>
+  </si>
+  <si>
     <t>2024/3/27</t>
   </si>
   <si>
     <t>上午第2节</t>
   </si>
   <si>
+    <t>课程A</t>
+  </si>
+  <si>
+    <t>班级1</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
@@ -109,12 +131,27 @@
     <t>2</t>
   </si>
   <si>
+    <t>教师B</t>
+  </si>
+  <si>
+    <t>教师AF</t>
+  </si>
+  <si>
+    <t>学院B</t>
+  </si>
+  <si>
     <t>2024/3/26</t>
   </si>
   <si>
     <t>上午第4节</t>
   </si>
   <si>
+    <t>课程B</t>
+  </si>
+  <si>
+    <t>班级2</t>
+  </si>
+  <si>
     <t>32</t>
   </si>
   <si>
@@ -133,21 +170,54 @@
     <t>3</t>
   </si>
   <si>
+    <t>教师C</t>
+  </si>
+  <si>
+    <t>教师AG</t>
+  </si>
+  <si>
+    <t>学院C</t>
+  </si>
+  <si>
     <t>下午第7节</t>
   </si>
   <si>
+    <t>课程C</t>
+  </si>
+  <si>
+    <t>班级3</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>教师D</t>
+  </si>
+  <si>
+    <t>教师AH</t>
+  </si>
+  <si>
+    <t>学院D</t>
+  </si>
+  <si>
     <t>2024/3/28</t>
   </si>
   <si>
     <t>下午第11节</t>
   </si>
   <si>
+    <t>课程D</t>
+  </si>
+  <si>
+    <t>班级4</t>
+  </si>
+  <si>
+    <t>学院J</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
@@ -166,9 +236,24 @@
     <t>5</t>
   </si>
   <si>
+    <t>教师E</t>
+  </si>
+  <si>
+    <t>教师AI</t>
+  </si>
+  <si>
+    <t>学院E</t>
+  </si>
+  <si>
     <t>上午第3节</t>
   </si>
   <si>
+    <t>课程E、课程F</t>
+  </si>
+  <si>
+    <t>班级5</t>
+  </si>
+  <si>
     <t>46</t>
   </si>
   <si>
@@ -187,9 +272,24 @@
     <t>6</t>
   </si>
   <si>
+    <t>教师F</t>
+  </si>
+  <si>
+    <t>教师AJ</t>
+  </si>
+  <si>
+    <t>学院F</t>
+  </si>
+  <si>
     <t>上午第1节</t>
   </si>
   <si>
+    <t>课程G</t>
+  </si>
+  <si>
+    <t>班级6</t>
+  </si>
+  <si>
     <t>33</t>
   </si>
   <si>
@@ -202,6 +302,15 @@
     <t>7</t>
   </si>
   <si>
+    <t>教师AK</t>
+  </si>
+  <si>
+    <t>课程H</t>
+  </si>
+  <si>
+    <t>班级7</t>
+  </si>
+  <si>
     <t>39</t>
   </si>
   <si>
@@ -214,16 +323,34 @@
     <t>8</t>
   </si>
   <si>
+    <t>教师G</t>
+  </si>
+  <si>
+    <t>教师AL</t>
+  </si>
+  <si>
     <t>2024/4/1</t>
   </si>
   <si>
+    <t>课程I</t>
+  </si>
+  <si>
+    <t>班级8</t>
+  </si>
+  <si>
     <t>45</t>
   </si>
   <si>
+    <t>教师H</t>
+  </si>
+  <si>
     <t>2024/4/2</t>
   </si>
   <si>
     <t>上午第5节</t>
+  </si>
+  <si>
+    <t>班级9</t>
   </si>
   <si>
     <t>29</t>
@@ -242,9 +369,24 @@
     <t>10</t>
   </si>
   <si>
+    <t>教师I</t>
+  </si>
+  <si>
+    <t>教师AM</t>
+  </si>
+  <si>
+    <t>学院G</t>
+  </si>
+  <si>
     <t>2024/3/29</t>
   </si>
   <si>
+    <t>课程J</t>
+  </si>
+  <si>
+    <t>班级10</t>
+  </si>
+  <si>
     <t>68</t>
   </si>
   <si>
@@ -258,6 +400,12 @@
   </si>
   <si>
     <t>11</t>
+  </si>
+  <si>
+    <t>教师J</t>
+  </si>
+  <si>
+    <t>教师AN</t>
   </si>
   <si>
     <t>2024/4/3</t>
@@ -277,9 +425,21 @@
     <t>12</t>
   </si>
   <si>
+    <t>教师K</t>
+  </si>
+  <si>
+    <t>教师AO</t>
+  </si>
+  <si>
     <t>2024/4/10</t>
   </si>
   <si>
+    <t>课程K</t>
+  </si>
+  <si>
+    <t>班级11</t>
+  </si>
+  <si>
     <t>54</t>
   </si>
   <si>
@@ -292,6 +452,12 @@
     <t>13</t>
   </si>
   <si>
+    <t>教师L</t>
+  </si>
+  <si>
+    <t>教师AP</t>
+  </si>
+  <si>
     <t>2024/4/16</t>
   </si>
   <si>
@@ -307,6 +473,15 @@
     <t>14</t>
   </si>
   <si>
+    <t>教师M</t>
+  </si>
+  <si>
+    <t>教师AQ</t>
+  </si>
+  <si>
+    <t>课程L</t>
+  </si>
+  <si>
     <t>70</t>
   </si>
   <si>
@@ -319,7 +494,19 @@
     <t>15</t>
   </si>
   <si>
+    <t>教师N</t>
+  </si>
+  <si>
+    <t>学院H</t>
+  </si>
+  <si>
     <t>2024/4/11</t>
+  </si>
+  <si>
+    <t>班级12</t>
+  </si>
+  <si>
+    <t>学院K</t>
   </si>
   <si>
     <t>1、学生扫码签到在屏幕上显示——能起到督促作用。
@@ -330,6 +517,9 @@
     <t>98</t>
   </si>
   <si>
+    <t>教师O</t>
+  </si>
+  <si>
     <t>下午第10节</t>
   </si>
   <si>
@@ -346,7 +536,17 @@
     <t>17</t>
   </si>
   <si>
+    <t>教师P</t>
+  </si>
+  <si>
+    <t>教师备课充分，讲授熟练，注重讲练结合，互动多，注重启发学生思考，课堂氛围活跃。、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>18</t>
+  </si>
+  <si>
+    <t>教师AR</t>
   </si>
   <si>
     <t>上午1-4节，6-7节</t>
@@ -360,12 +560,21 @@
     <t>19</t>
   </si>
   <si>
+    <t>教师Q</t>
+  </si>
+  <si>
     <t>0.620689655172414</t>
   </si>
   <si>
     <t>备课充分，讲课熟练。概念原理表达准确，合理使用板书，授课效果较好。讲授较为生动，有一定的启发性。</t>
   </si>
   <si>
+    <t>教师R</t>
+  </si>
+  <si>
+    <t>班级13、班级14</t>
+  </si>
+  <si>
     <t>65</t>
   </si>
   <si>
@@ -375,15 +584,30 @@
     <t>备课充分，讲课熟练。合理使用板书，教学效果较好。讲课时精神饱满，有一定吸引力。</t>
   </si>
   <si>
+    <t>教师S</t>
+  </si>
+  <si>
     <t>2024/4/7</t>
   </si>
   <si>
+    <t>班级13、班级15</t>
+  </si>
+  <si>
     <t>57</t>
   </si>
   <si>
+    <t xml:space="preserve">
+老师备课充分、熟练，表达准确。条例清晰，板书工整，课堂气氛一般，互动一般。
+建议：是否可以提醒和督促旷课和迟到的学生？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>93</t>
   </si>
   <si>
+    <t>教师T</t>
+  </si>
+  <si>
     <t>71</t>
   </si>
   <si>
@@ -408,18 +632,39 @@
     <t>24</t>
   </si>
   <si>
+    <t>教师AS</t>
+  </si>
+  <si>
     <t>2024/5/9</t>
   </si>
   <si>
+    <t>课程M</t>
+  </si>
+  <si>
+    <t>班级16</t>
+  </si>
+  <si>
     <t>全英文授课课程，教师英语表述流畅，语速适当，讲授条理清晰，注重理论结合实际，举例恰当。互动较少，课堂安静。</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
+    <t>教师AT</t>
+  </si>
+  <si>
+    <t>学院I</t>
+  </si>
+  <si>
     <t>2024/5/15</t>
   </si>
   <si>
+    <t>课程N</t>
+  </si>
+  <si>
+    <t>班级17</t>
+  </si>
+  <si>
     <t>34</t>
   </si>
   <si>
@@ -432,6 +677,9 @@
     <t>26</t>
   </si>
   <si>
+    <t>教师U</t>
+  </si>
+  <si>
     <t>2024/5/8</t>
   </si>
   <si>
@@ -441,21 +689,61 @@
     <t>27</t>
   </si>
   <si>
+    <t>教师AU</t>
+  </si>
+  <si>
     <t>0.909090909090909</t>
   </si>
   <si>
+    <t>教学目的明确，通过游戏完成指定任务，让学生锻炼增强相互之间的沟通能力，领导能力，从而到达和谐完成任务的目的，期间教师及时点评，引导。课堂气氛活跃，师生互动好，教学效果好。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教师AV</t>
+  </si>
+  <si>
+    <t>课程O</t>
+  </si>
+  <si>
     <t>脱稿讲授，利用手机进行线上测试现场布置的作业，中英文结合讲测试题，课堂中开展小组讨论等多种教学方法，师生互动频繁。建议适当增加板书。</t>
   </si>
   <si>
+    <t>教师V</t>
+  </si>
+  <si>
+    <t>教师AW</t>
+  </si>
+  <si>
+    <t>课程P</t>
+  </si>
+  <si>
+    <t>班级18</t>
+  </si>
+  <si>
+    <t>学院L</t>
+  </si>
+  <si>
     <t>77</t>
   </si>
   <si>
     <t>备课充分，板书多，讲课生动、投入，进行课堂讨论，做题及时掌握学生的知识程度。有互动提问，教学效果好。</t>
   </si>
   <si>
+    <t>教师W</t>
+  </si>
+  <si>
+    <t>教师AX</t>
+  </si>
+  <si>
     <t>2024/4/28</t>
   </si>
   <si>
+    <t>课程Q</t>
+  </si>
+  <si>
+    <t>班级19</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
@@ -469,6 +757,15 @@
   </si>
   <si>
     <t>91</t>
+  </si>
+  <si>
+    <t>教师X</t>
+  </si>
+  <si>
+    <t>教师AY</t>
+  </si>
+  <si>
+    <t>班级20</t>
   </si>
   <si>
     <t>84</t>
@@ -487,21 +784,42 @@
 教态教姿方面，教态端正，上课精神饱满，授课状态好。</t>
   </si>
   <si>
+    <t>教师Y</t>
+  </si>
+  <si>
+    <t>教师AZ</t>
+  </si>
+  <si>
     <t>2024/5/27</t>
   </si>
   <si>
     <t>下午第6节</t>
   </si>
   <si>
+    <t>课程R</t>
+  </si>
+  <si>
+    <t>班级21</t>
+  </si>
+  <si>
     <t>0.964285714285714</t>
   </si>
   <si>
     <t>备课充分，板书与PPT相结合。课内讲授与学生练习相结合。师生互动好，课堂纪律好。建议以PPT全屏展示，方便学生观看。</t>
   </si>
   <si>
+    <t>教师Z</t>
+  </si>
+  <si>
+    <t>教师BA</t>
+  </si>
+  <si>
     <t>2024/3/25</t>
   </si>
   <si>
+    <t>班级22</t>
+  </si>
+  <si>
     <t>43</t>
   </si>
   <si>
@@ -514,15 +832,31 @@
     <t>35</t>
   </si>
   <si>
+    <t>教师AA</t>
+  </si>
+  <si>
+    <t>教师BB</t>
+  </si>
+  <si>
     <t>2024/5/28</t>
   </si>
   <si>
-    <t>教师讲解中国度娘壁画的要素、色彩、线条、表现形式，带领学生边讲解边完成飞天造型。讲课形象生动，案例分析讲解到位，互动良好。</t>
+    <t>课程S</t>
+  </si>
+  <si>
+    <t>教师讲解中国壁画的要素、色彩、线条、表现形式，带领学生边讲解边完成飞天造型。讲课形象生动，案例分析讲解到位，互动良好。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>36</t>
   </si>
   <si>
+    <t>教师AB</t>
+  </si>
+  <si>
+    <t>班级23</t>
+  </si>
+  <si>
     <t>56</t>
   </si>
   <si>
@@ -532,10 +866,25 @@
     <t>37</t>
   </si>
   <si>
+    <t>教师AC</t>
+  </si>
+  <si>
+    <t>课程T</t>
+  </si>
+  <si>
+    <t>班级24</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
     <t>38</t>
+  </si>
+  <si>
+    <t>教师AD</t>
+  </si>
+  <si>
+    <t>教师BC</t>
   </si>
   <si>
     <t>0.882352941176471</t>
@@ -543,351 +892,6 @@
   <si>
     <t>教师讲课重点突出，条理清晰，讲授熟练，使用中外文混合行进行知识点讲解。善于用直观、形象的例子解释所讲内容。多媒体课件设计合理。教学方法有所创新，教学中理论联系实际，讲练
 结合。课堂气氛活跃，师生互动很好。善于启发学生，学生参与课堂教学活动积极性很高，师生关系融洽。</t>
-  </si>
-  <si>
-    <t>公司A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>教师A</t>
-  </si>
-  <si>
-    <t>教师AE</t>
-  </si>
-  <si>
-    <t>学院A</t>
-  </si>
-  <si>
-    <t>教师B</t>
-  </si>
-  <si>
-    <t>教师AF</t>
-  </si>
-  <si>
-    <t>学院B</t>
-  </si>
-  <si>
-    <t>教师C</t>
-  </si>
-  <si>
-    <t>教师AG</t>
-  </si>
-  <si>
-    <t>学院C</t>
-  </si>
-  <si>
-    <t>教师D</t>
-  </si>
-  <si>
-    <t>教师AH</t>
-  </si>
-  <si>
-    <t>学院D</t>
-  </si>
-  <si>
-    <t>教师E</t>
-  </si>
-  <si>
-    <t>教师AI</t>
-  </si>
-  <si>
-    <t>学院E</t>
-  </si>
-  <si>
-    <t>教师F</t>
-  </si>
-  <si>
-    <t>教师AJ</t>
-  </si>
-  <si>
-    <t>学院F</t>
-  </si>
-  <si>
-    <t>教师AK</t>
-  </si>
-  <si>
-    <t>教师G</t>
-  </si>
-  <si>
-    <t>教师AL</t>
-  </si>
-  <si>
-    <t>教师H</t>
-  </si>
-  <si>
-    <t>教师I</t>
-  </si>
-  <si>
-    <t>教师AM</t>
-  </si>
-  <si>
-    <t>学院G</t>
-  </si>
-  <si>
-    <t>教师J</t>
-  </si>
-  <si>
-    <t>教师AN</t>
-  </si>
-  <si>
-    <t>教师K</t>
-  </si>
-  <si>
-    <t>教师AO</t>
-  </si>
-  <si>
-    <t>教师L</t>
-  </si>
-  <si>
-    <t>教师AP</t>
-  </si>
-  <si>
-    <t>教师M</t>
-  </si>
-  <si>
-    <t>教师AQ</t>
-  </si>
-  <si>
-    <t>教师N</t>
-  </si>
-  <si>
-    <t>学院H</t>
-  </si>
-  <si>
-    <t>教师O</t>
-  </si>
-  <si>
-    <t>教师P</t>
-  </si>
-  <si>
-    <t>教师AR</t>
-  </si>
-  <si>
-    <t>教师Q</t>
-  </si>
-  <si>
-    <t>教师R</t>
-  </si>
-  <si>
-    <t>教师S</t>
-  </si>
-  <si>
-    <t>教师T</t>
-  </si>
-  <si>
-    <t>教师AS</t>
-  </si>
-  <si>
-    <t>教师AT</t>
-  </si>
-  <si>
-    <t>学院I</t>
-  </si>
-  <si>
-    <t>教师U</t>
-  </si>
-  <si>
-    <t>教师AU</t>
-  </si>
-  <si>
-    <t>教师AV</t>
-  </si>
-  <si>
-    <t>教师V</t>
-  </si>
-  <si>
-    <t>教师AW</t>
-  </si>
-  <si>
-    <t>教师W</t>
-  </si>
-  <si>
-    <t>教师AX</t>
-  </si>
-  <si>
-    <t>教师X</t>
-  </si>
-  <si>
-    <t>教师AY</t>
-  </si>
-  <si>
-    <t>教师Y</t>
-  </si>
-  <si>
-    <t>教师AZ</t>
-  </si>
-  <si>
-    <t>教师Z</t>
-  </si>
-  <si>
-    <t>教师BA</t>
-  </si>
-  <si>
-    <t>教师AA</t>
-  </si>
-  <si>
-    <t>教师BB</t>
-  </si>
-  <si>
-    <t>教师AB</t>
-  </si>
-  <si>
-    <t>教师AC</t>
-  </si>
-  <si>
-    <t>教师AD</t>
-  </si>
-  <si>
-    <t>教师BC</t>
-  </si>
-  <si>
-    <t>课程A</t>
-  </si>
-  <si>
-    <t>班级1</t>
-  </si>
-  <si>
-    <t>课程B</t>
-  </si>
-  <si>
-    <t>班级2</t>
-  </si>
-  <si>
-    <t>课程C</t>
-  </si>
-  <si>
-    <t>班级3</t>
-  </si>
-  <si>
-    <t>课程D</t>
-  </si>
-  <si>
-    <t>班级4</t>
-  </si>
-  <si>
-    <t>学院J</t>
-  </si>
-  <si>
-    <t>课程E、课程F</t>
-  </si>
-  <si>
-    <t>班级5</t>
-  </si>
-  <si>
-    <t>课程G</t>
-  </si>
-  <si>
-    <t>班级6</t>
-  </si>
-  <si>
-    <t>课程H</t>
-  </si>
-  <si>
-    <t>班级7</t>
-  </si>
-  <si>
-    <t>课程I</t>
-  </si>
-  <si>
-    <t>班级8</t>
-  </si>
-  <si>
-    <t>班级9</t>
-  </si>
-  <si>
-    <t>课程J</t>
-  </si>
-  <si>
-    <t>班级10</t>
-  </si>
-  <si>
-    <t>课程K</t>
-  </si>
-  <si>
-    <t>班级11</t>
-  </si>
-  <si>
-    <t>课程L</t>
-  </si>
-  <si>
-    <t>班级12</t>
-  </si>
-  <si>
-    <t>学院K</t>
-  </si>
-  <si>
-    <t>班级13、班级14</t>
-  </si>
-  <si>
-    <t>班级13、班级15</t>
-  </si>
-  <si>
-    <t>课程M</t>
-  </si>
-  <si>
-    <t>班级16</t>
-  </si>
-  <si>
-    <t>课程N</t>
-  </si>
-  <si>
-    <t>班级17</t>
-  </si>
-  <si>
-    <t>课程O</t>
-  </si>
-  <si>
-    <t>课程P</t>
-  </si>
-  <si>
-    <t>班级18</t>
-  </si>
-  <si>
-    <t>学院L</t>
-  </si>
-  <si>
-    <t>课程Q</t>
-  </si>
-  <si>
-    <t>班级19</t>
-  </si>
-  <si>
-    <t>班级20</t>
-  </si>
-  <si>
-    <t>课程R</t>
-  </si>
-  <si>
-    <t>班级21</t>
-  </si>
-  <si>
-    <t>班级22</t>
-  </si>
-  <si>
-    <t>课程S</t>
-  </si>
-  <si>
-    <t>班级23</t>
-  </si>
-  <si>
-    <t>课程T</t>
-  </si>
-  <si>
-    <t>班级24</t>
-  </si>
-  <si>
-    <t>教师备课充分，讲授熟练，注重讲练结合，互动多，注重启发学生思考，课堂氛围活跃。、</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-老师备课充分、熟练，表达准确。条例清晰，板书工整，课堂气氛一般，互动一般。
-建议：是否可以提醒和督促旷课和迟到的学生？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>教学目的明确，通过游戏完成指定任务，让学生锻炼增强相互之间的沟通能力，领导能力，从而到达和谐完成任务的目的，期间教师及时点评，引导。课堂气氛活跃，师生互动好，教学效果好。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1235,1931 +1239,1931 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>230</v>
-      </c>
-      <c r="H4" t="s">
-        <v>231</v>
-      </c>
-      <c r="I4" t="s">
-        <v>168</v>
-      </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>232</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="P5" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="Q5" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>234</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s">
-        <v>235</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="M6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q6" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>236</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
-        <v>237</v>
+        <v>57</v>
       </c>
       <c r="I7" t="s">
-        <v>238</v>
+        <v>58</v>
       </c>
       <c r="J7" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="K7" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="L7" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="M7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="O7" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="P7" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="Q7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="G8" t="s">
-        <v>239</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>238</v>
+        <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="K8" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="L8" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="N8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O8" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="P8" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="Q8" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O9" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="Q9" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" t="s">
+        <v>90</v>
+      </c>
+      <c r="L10" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" t="s">
         <v>17</v>
       </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" t="s">
-        <v>243</v>
-      </c>
-      <c r="H10" t="s">
-        <v>244</v>
-      </c>
-      <c r="I10" t="s">
-        <v>238</v>
-      </c>
-      <c r="K10" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" t="s">
-        <v>55</v>
-      </c>
-      <c r="M10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O10" t="s">
-        <v>16</v>
-      </c>
       <c r="P10" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="Q10" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>245</v>
+        <v>97</v>
       </c>
       <c r="H11" t="s">
-        <v>246</v>
+        <v>98</v>
       </c>
       <c r="I11" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K11" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="L11" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="M11" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N11" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>185</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="G12" t="s">
-        <v>232</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>247</v>
+        <v>103</v>
       </c>
       <c r="I12" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K12" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="L12" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N12" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O12" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="P12" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="Q12" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>188</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>248</v>
+        <v>113</v>
       </c>
       <c r="H13" t="s">
-        <v>249</v>
+        <v>114</v>
       </c>
       <c r="I13" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="K13" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="L13" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="M13" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O13" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="P13" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="Q13" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>191</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>230</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="I14" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N14" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="O14" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="P14" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="Q14" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="H15" t="s">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="I15" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="K15" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="L15" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="M15" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P15" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="Q15" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>234</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
-        <v>235</v>
+        <v>48</v>
       </c>
       <c r="I16" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="N16" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="O16" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="P16" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="Q16" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>143</v>
       </c>
       <c r="C17" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="D17" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>252</v>
+        <v>145</v>
       </c>
       <c r="H17" t="s">
-        <v>249</v>
+        <v>114</v>
       </c>
       <c r="I17" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="K17" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="L17" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="M17" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="Q17" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C18" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="G18" t="s">
-        <v>239</v>
+        <v>69</v>
       </c>
       <c r="H18" t="s">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="I18" t="s">
-        <v>254</v>
+        <v>154</v>
       </c>
       <c r="K18" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="L18" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="M18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P18" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="Q18" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="F19" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="G19" t="s">
-        <v>236</v>
+        <v>56</v>
       </c>
       <c r="H19" t="s">
-        <v>237</v>
+        <v>57</v>
       </c>
       <c r="I19" t="s">
-        <v>238</v>
+        <v>58</v>
       </c>
       <c r="K19" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="L19" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="N19" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="O19" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="P19" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="Q19" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>239</v>
+        <v>69</v>
       </c>
       <c r="H20" t="s">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="I20" t="s">
-        <v>254</v>
+        <v>154</v>
       </c>
       <c r="K20" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="L20" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="N20" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P20" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="Q20" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" t="s">
         <v>101</v>
       </c>
-      <c r="B21" t="s">
-        <v>191</v>
-      </c>
-      <c r="C21" t="s">
-        <v>203</v>
-      </c>
-      <c r="D21" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" t="s">
-        <v>61</v>
-      </c>
       <c r="F21" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="G21" t="s">
-        <v>234</v>
+        <v>47</v>
       </c>
       <c r="H21" t="s">
-        <v>235</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="N21" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P21" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="Q21" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" t="s">
+        <v>158</v>
+      </c>
+      <c r="G22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" t="s">
         <v>104</v>
       </c>
-      <c r="B22" t="s">
-        <v>204</v>
-      </c>
-      <c r="C22" t="s">
-        <v>176</v>
-      </c>
-      <c r="D22" t="s">
-        <v>177</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" t="s">
-        <v>236</v>
-      </c>
-      <c r="H22" t="s">
-        <v>237</v>
-      </c>
-      <c r="I22" t="s">
-        <v>238</v>
-      </c>
-      <c r="K22" t="s">
-        <v>63</v>
-      </c>
       <c r="L22" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N22" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="O22" t="s">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="P22" t="s">
-        <v>106</v>
+        <v>172</v>
       </c>
       <c r="Q22" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="C23" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="F23" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>248</v>
+        <v>113</v>
       </c>
       <c r="H23" t="s">
-        <v>255</v>
+        <v>174</v>
       </c>
       <c r="I23" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="K23" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="L23" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="M23" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="N23" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O23" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="P23" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="Q23" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="C24" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="F24" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>248</v>
+        <v>113</v>
       </c>
       <c r="H24" t="s">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="I24" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="K24" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="L24" t="s">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="M24" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="N24" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="P24" t="s">
-        <v>276</v>
+        <v>182</v>
       </c>
       <c r="Q24" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="G25" t="s">
-        <v>252</v>
+        <v>145</v>
       </c>
       <c r="H25" t="s">
-        <v>249</v>
+        <v>114</v>
       </c>
       <c r="I25" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="K25" t="s">
-        <v>113</v>
+        <v>185</v>
       </c>
       <c r="L25" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="M25" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="N25" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="O25" t="s">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="P25" t="s">
-        <v>116</v>
+        <v>188</v>
       </c>
       <c r="Q25" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="C26" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" t="s">
+        <v>145</v>
+      </c>
+      <c r="H26" t="s">
+        <v>114</v>
+      </c>
+      <c r="I26" t="s">
+        <v>111</v>
+      </c>
+      <c r="K26" t="s">
+        <v>189</v>
+      </c>
+      <c r="L26" t="s">
+        <v>186</v>
+      </c>
+      <c r="M26" t="s">
+        <v>139</v>
+      </c>
+      <c r="N26" t="s">
+        <v>135</v>
+      </c>
+      <c r="O26" t="s">
         <v>190</v>
       </c>
-      <c r="E26" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26" t="s">
-        <v>252</v>
-      </c>
-      <c r="H26" t="s">
-        <v>249</v>
-      </c>
-      <c r="I26" t="s">
-        <v>190</v>
-      </c>
-      <c r="K26" t="s">
-        <v>117</v>
-      </c>
-      <c r="L26" t="s">
-        <v>114</v>
-      </c>
-      <c r="M26" t="s">
-        <v>85</v>
-      </c>
-      <c r="N26" t="s">
-        <v>83</v>
-      </c>
-      <c r="O26" t="s">
-        <v>118</v>
-      </c>
       <c r="P26" t="s">
-        <v>119</v>
+        <v>191</v>
       </c>
       <c r="Q26" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="B27" t="s">
-        <v>185</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="D27" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>194</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="G27" t="s">
-        <v>257</v>
+        <v>195</v>
       </c>
       <c r="H27" t="s">
-        <v>258</v>
+        <v>196</v>
       </c>
       <c r="I27" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K27" t="s">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="L27" t="s">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="M27" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P27" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="Q27" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D28" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E28" t="s">
-        <v>124</v>
+        <v>201</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="H28" t="s">
-        <v>260</v>
+        <v>203</v>
       </c>
       <c r="I28" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="K28" t="s">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="L28" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="M28" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="O28" t="s">
-        <v>127</v>
+        <v>206</v>
       </c>
       <c r="Q28" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>207</v>
       </c>
       <c r="B29" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C29" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29" t="s">
+        <v>200</v>
+      </c>
+      <c r="E29" t="s">
         <v>209</v>
       </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s">
+        <v>202</v>
+      </c>
+      <c r="H29" t="s">
+        <v>203</v>
+      </c>
+      <c r="I29" t="s">
+        <v>200</v>
+      </c>
+      <c r="K29" t="s">
+        <v>204</v>
+      </c>
+      <c r="L29" t="s">
+        <v>205</v>
+      </c>
+      <c r="M29" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" t="s">
+        <v>76</v>
+      </c>
+      <c r="O29" t="s">
+        <v>206</v>
+      </c>
+      <c r="P29" t="s">
         <v>210</v>
       </c>
-      <c r="E29" t="s">
-        <v>129</v>
-      </c>
-      <c r="F29" t="s">
-        <v>50</v>
-      </c>
-      <c r="G29" t="s">
-        <v>259</v>
-      </c>
-      <c r="H29" t="s">
-        <v>260</v>
-      </c>
-      <c r="I29" t="s">
-        <v>210</v>
-      </c>
-      <c r="K29" t="s">
-        <v>125</v>
-      </c>
-      <c r="L29" t="s">
-        <v>126</v>
-      </c>
-      <c r="M29" t="s">
-        <v>20</v>
-      </c>
-      <c r="N29" t="s">
-        <v>49</v>
-      </c>
-      <c r="O29" t="s">
-        <v>127</v>
-      </c>
-      <c r="P29" t="s">
-        <v>130</v>
-      </c>
       <c r="Q29" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="B30" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C30" t="s">
         <v>212</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="F30" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s">
-        <v>230</v>
+        <v>23</v>
       </c>
       <c r="H30" t="s">
-        <v>231</v>
+        <v>24</v>
       </c>
       <c r="I30" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L30" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="M30" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="N30" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O30" t="s">
-        <v>132</v>
+        <v>213</v>
       </c>
       <c r="P30" t="s">
-        <v>277</v>
+        <v>214</v>
       </c>
       <c r="Q30" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="H31" t="s">
-        <v>246</v>
+        <v>98</v>
       </c>
       <c r="I31" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K31" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="L31" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="M31" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="N31" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P31" t="s">
-        <v>133</v>
+        <v>217</v>
       </c>
       <c r="Q31" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C32" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D32" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="G32" t="s">
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="H32" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="I32" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="K32" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="L32" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="M32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P32" t="s">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="Q32" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:17">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C33" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
-        <v>136</v>
+        <v>227</v>
       </c>
       <c r="F33" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="G33" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="H33" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="I33" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K33" t="s">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="L33" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O33" t="s">
-        <v>138</v>
+        <v>231</v>
       </c>
       <c r="Q33" t="s">
-        <v>139</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:17">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D34" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="F34" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="G34" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="H34" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="I34" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K34" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="L34" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="M34" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P34" t="s">
-        <v>140</v>
+        <v>233</v>
       </c>
       <c r="Q34" t="s">
-        <v>141</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" t="s">
+        <v>236</v>
+      </c>
+      <c r="D35" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" t="s">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s">
+        <v>220</v>
+      </c>
+      <c r="H35" t="s">
+        <v>237</v>
+      </c>
+      <c r="I35" t="s">
+        <v>222</v>
+      </c>
+      <c r="K35" t="s">
+        <v>238</v>
+      </c>
+      <c r="L35" t="s">
+        <v>239</v>
+      </c>
+      <c r="M35" t="s">
         <v>26</v>
       </c>
-      <c r="B35" t="s">
-        <v>218</v>
-      </c>
-      <c r="C35" t="s">
-        <v>219</v>
-      </c>
-      <c r="D35" t="s">
-        <v>190</v>
-      </c>
-      <c r="E35" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" t="s">
-        <v>50</v>
-      </c>
-      <c r="G35" t="s">
-        <v>262</v>
-      </c>
-      <c r="H35" t="s">
-        <v>267</v>
-      </c>
-      <c r="I35" t="s">
-        <v>264</v>
-      </c>
-      <c r="K35" t="s">
-        <v>142</v>
-      </c>
-      <c r="L35" t="s">
-        <v>143</v>
-      </c>
-      <c r="M35" t="s">
-        <v>20</v>
-      </c>
       <c r="N35" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O35" t="s">
-        <v>144</v>
+        <v>240</v>
       </c>
       <c r="P35" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="Q35" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:17">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C36" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="D36" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E36" t="s">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c r="F36" t="s">
-        <v>147</v>
+        <v>245</v>
       </c>
       <c r="G36" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="H36" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="I36" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="K36" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="L36" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="M36" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O36" t="s">
-        <v>148</v>
+        <v>248</v>
       </c>
       <c r="P36" t="s">
-        <v>149</v>
+        <v>249</v>
       </c>
       <c r="Q36" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="C37" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="D37" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>150</v>
+        <v>252</v>
       </c>
       <c r="F37" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="G37" t="s">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="H37" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="I37" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K37" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="L37" t="s">
-        <v>151</v>
+        <v>254</v>
       </c>
       <c r="M37" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O37" t="s">
-        <v>152</v>
+        <v>255</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>256</v>
       </c>
       <c r="Q37" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>257</v>
       </c>
       <c r="B38" t="s">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="D38" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E38" t="s">
-        <v>155</v>
+        <v>260</v>
       </c>
       <c r="F38" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G38" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="H38" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="I38" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="K38" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="L38" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="M38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P38" t="s">
-        <v>156</v>
+        <v>262</v>
       </c>
       <c r="Q38" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="B39" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="C39" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="F39" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="G39" t="s">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="H39" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="I39" t="s">
-        <v>254</v>
+        <v>154</v>
       </c>
       <c r="K39" t="s">
-        <v>158</v>
+        <v>266</v>
       </c>
       <c r="L39" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="M39" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="N39" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O39" t="s">
-        <v>148</v>
+        <v>248</v>
       </c>
       <c r="P39" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
       <c r="Q39" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
       <c r="B40" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="C40" t="s">
-        <v>169</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="E40" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="F40" t="s">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s">
+        <v>270</v>
+      </c>
+      <c r="H40" t="s">
+        <v>271</v>
+      </c>
+      <c r="I40" t="s">
+        <v>154</v>
+      </c>
+      <c r="K40" t="s">
+        <v>72</v>
+      </c>
+      <c r="L40" t="s">
+        <v>272</v>
+      </c>
+      <c r="N40" t="s">
         <v>50</v>
       </c>
-      <c r="G40" t="s">
-        <v>273</v>
-      </c>
-      <c r="H40" t="s">
-        <v>274</v>
-      </c>
-      <c r="I40" t="s">
-        <v>254</v>
-      </c>
-      <c r="K40" t="s">
-        <v>45</v>
-      </c>
-      <c r="L40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N40" t="s">
-        <v>34</v>
-      </c>
       <c r="O40" t="s">
-        <v>132</v>
+        <v>213</v>
       </c>
       <c r="Q40" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" t="s">
-        <v>162</v>
+        <v>273</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="C41" t="s">
-        <v>229</v>
+        <v>275</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="E41" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="F41" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G41" t="s">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="K41" t="s">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="L41" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="N41" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O41" t="s">
-        <v>163</v>
+        <v>276</v>
       </c>
       <c r="P41" t="s">
-        <v>164</v>
+        <v>277</v>
       </c>
       <c r="Q41" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -3171,7 +3175,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3181,7 +3185,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3189,6 +3193,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -3336,29 +3355,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D42314C-5EEB-42DF-8712-F88FFA52587A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{606661BE-E121-44A1-81CB-AFC8DECC49A7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{427EE740-0FF9-4C4A-84FA-F05DB4A67B53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9154763-3E0D-43E9-8963-AAD70AB074B9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA507F5F-7224-4210-B803-1337B24B738E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09DDA65D-2B00-4E74-8DC9-9E92DB0F7BA3}"/>
 </file>